--- a/Design/config/CityLevelConfig.xlsx
+++ b/Design/config/CityLevelConfig.xlsx
@@ -568,15 +568,15 @@
         <v>100</v>
       </c>
       <c r="C5" s="4">
-        <f>10+(INT($A5/10))</f>
+        <f t="shared" ref="C5:E24" si="0">10+(INT($A5/10))</f>
         <v>10</v>
       </c>
       <c r="D5" s="4">
-        <f>10+(INT($A5/10))</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="E5" s="4">
-        <f>10+(INT($A5/10))</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
@@ -585,18 +585,18 @@
         <v>2</v>
       </c>
       <c r="B6" s="4">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="C6" s="4">
-        <f>10+(INT($A6/10))</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="D6" s="4">
-        <f>10+(INT($A6/10))</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="E6" s="4">
-        <f>10+(INT($A6/10))</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
@@ -605,18 +605,18 @@
         <v>3</v>
       </c>
       <c r="B7" s="4">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="C7" s="4">
-        <f>10+(INT($A7/10))</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="D7" s="4">
-        <f>10+(INT($A7/10))</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="E7" s="4">
-        <f>10+(INT($A7/10))</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="V7" s="5"/>
@@ -627,18 +627,18 @@
         <v>4</v>
       </c>
       <c r="B8" s="4">
-        <v>100</v>
+        <v>130</v>
       </c>
       <c r="C8" s="4">
-        <f>10+(INT($A8/10))</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="D8" s="4">
-        <f>10+(INT($A8/10))</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="E8" s="4">
-        <f>10+(INT($A8/10))</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
@@ -647,18 +647,18 @@
         <v>5</v>
       </c>
       <c r="B9" s="4">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="C9" s="4">
-        <f>10+(INT($A9/10))</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="D9" s="4">
-        <f>10+(INT($A9/10))</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="E9" s="4">
-        <f>10+(INT($A9/10))</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
@@ -667,18 +667,18 @@
         <v>6</v>
       </c>
       <c r="B10" s="4">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="C10" s="4">
-        <f>10+(INT($A10/10))</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="D10" s="4">
-        <f>10+(INT($A10/10))</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="E10" s="4">
-        <f>10+(INT($A10/10))</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
@@ -687,18 +687,18 @@
         <v>7</v>
       </c>
       <c r="B11" s="4">
-        <v>100</v>
+        <v>160</v>
       </c>
       <c r="C11" s="4">
-        <f>10+(INT($A11/10))</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="D11" s="4">
-        <f>10+(INT($A11/10))</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="E11" s="4">
-        <f>10+(INT($A11/10))</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
@@ -707,18 +707,18 @@
         <v>8</v>
       </c>
       <c r="B12" s="4">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="C12" s="4">
-        <f>10+(INT($A12/10))</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="D12" s="4">
-        <f>10+(INT($A12/10))</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="E12" s="4">
-        <f>10+(INT($A12/10))</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
@@ -727,18 +727,18 @@
         <v>9</v>
       </c>
       <c r="B13" s="4">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="C13" s="4">
-        <f>10+(INT($A13/10))</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="D13" s="4">
-        <f>10+(INT($A13/10))</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="E13" s="4">
-        <f>10+(INT($A13/10))</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
     </row>
@@ -747,18 +747,18 @@
         <v>10</v>
       </c>
       <c r="B14" s="4">
-        <v>100</v>
+        <v>190</v>
       </c>
       <c r="C14" s="4">
-        <f>10+(INT($A14/10))</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="D14" s="4">
-        <f>10+(INT($A14/10))</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="E14" s="4">
-        <f>10+(INT($A14/10))</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
     </row>
@@ -767,18 +767,18 @@
         <v>11</v>
       </c>
       <c r="B15" s="4">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="C15" s="4">
-        <f>10+(INT($A15/10))</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="D15" s="4">
-        <f>10+(INT($A15/10))</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="E15" s="4">
-        <f>10+(INT($A15/10))</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
     </row>
@@ -787,18 +787,18 @@
         <v>12</v>
       </c>
       <c r="B16" s="4">
-        <v>100</v>
+        <v>210</v>
       </c>
       <c r="C16" s="4">
-        <f>10+(INT($A16/10))</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="D16" s="4">
-        <f>10+(INT($A16/10))</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="E16" s="4">
-        <f>10+(INT($A16/10))</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
     </row>
@@ -807,18 +807,18 @@
         <v>13</v>
       </c>
       <c r="B17" s="4">
-        <v>100</v>
+        <v>220</v>
       </c>
       <c r="C17" s="4">
-        <f>10+(INT($A17/10))</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="D17" s="4">
-        <f>10+(INT($A17/10))</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="E17" s="4">
-        <f>10+(INT($A17/10))</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
     </row>
@@ -827,18 +827,18 @@
         <v>14</v>
       </c>
       <c r="B18" s="4">
-        <v>100</v>
+        <v>230</v>
       </c>
       <c r="C18" s="4">
-        <f>10+(INT($A18/10))</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="D18" s="4">
-        <f>10+(INT($A18/10))</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="E18" s="4">
-        <f>10+(INT($A18/10))</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
     </row>
@@ -847,18 +847,18 @@
         <v>15</v>
       </c>
       <c r="B19" s="4">
-        <v>100</v>
+        <v>240</v>
       </c>
       <c r="C19" s="4">
-        <f>10+(INT($A19/10))</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="D19" s="4">
-        <f>10+(INT($A19/10))</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="E19" s="4">
-        <f>10+(INT($A19/10))</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
     </row>
@@ -867,18 +867,18 @@
         <v>16</v>
       </c>
       <c r="B20" s="4">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="C20" s="4">
-        <f>10+(INT($A20/10))</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="D20" s="4">
-        <f>10+(INT($A20/10))</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="E20" s="4">
-        <f>10+(INT($A20/10))</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
     </row>
@@ -887,18 +887,18 @@
         <v>17</v>
       </c>
       <c r="B21" s="4">
-        <v>100</v>
+        <v>260</v>
       </c>
       <c r="C21" s="4">
-        <f>10+(INT($A21/10))</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="D21" s="4">
-        <f>10+(INT($A21/10))</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="E21" s="4">
-        <f>10+(INT($A21/10))</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
     </row>
@@ -907,18 +907,18 @@
         <v>18</v>
       </c>
       <c r="B22" s="4">
-        <v>100</v>
+        <v>270</v>
       </c>
       <c r="C22" s="4">
-        <f>10+(INT($A22/10))</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="D22" s="4">
-        <f>10+(INT($A22/10))</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="E22" s="4">
-        <f>10+(INT($A22/10))</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
     </row>
@@ -927,18 +927,18 @@
         <v>19</v>
       </c>
       <c r="B23" s="4">
-        <v>100</v>
+        <v>280</v>
       </c>
       <c r="C23" s="4">
-        <f>10+(INT($A23/10))</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="D23" s="4">
-        <f>10+(INT($A23/10))</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="E23" s="4">
-        <f>10+(INT($A23/10))</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
     </row>
@@ -947,18 +947,18 @@
         <v>20</v>
       </c>
       <c r="B24" s="4">
-        <v>100</v>
+        <v>290</v>
       </c>
       <c r="C24" s="4">
-        <f>10+(INT($A24/10))</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="D24" s="4">
-        <f>10+(INT($A24/10))</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="E24" s="4">
-        <f>10+(INT($A24/10))</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
     </row>
@@ -967,18 +967,18 @@
         <v>21</v>
       </c>
       <c r="B25" s="4">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="C25" s="4">
-        <f>10+(INT($A25/10))</f>
+        <f t="shared" ref="C25:E44" si="1">10+(INT($A25/10))</f>
         <v>12</v>
       </c>
       <c r="D25" s="4">
-        <f>10+(INT($A25/10))</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="E25" s="4">
-        <f>10+(INT($A25/10))</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
     </row>
@@ -987,18 +987,18 @@
         <v>22</v>
       </c>
       <c r="B26" s="4">
-        <v>100</v>
+        <v>310</v>
       </c>
       <c r="C26" s="4">
-        <f>10+(INT($A26/10))</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="D26" s="4">
-        <f>10+(INT($A26/10))</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="E26" s="4">
-        <f>10+(INT($A26/10))</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
     </row>
@@ -1007,18 +1007,18 @@
         <v>23</v>
       </c>
       <c r="B27" s="4">
-        <v>100</v>
+        <v>320</v>
       </c>
       <c r="C27" s="4">
-        <f>10+(INT($A27/10))</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="D27" s="4">
-        <f>10+(INT($A27/10))</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="E27" s="4">
-        <f>10+(INT($A27/10))</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
     </row>
@@ -1027,18 +1027,18 @@
         <v>24</v>
       </c>
       <c r="B28" s="4">
-        <v>100</v>
+        <v>330</v>
       </c>
       <c r="C28" s="4">
-        <f>10+(INT($A28/10))</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="D28" s="4">
-        <f>10+(INT($A28/10))</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="E28" s="4">
-        <f>10+(INT($A28/10))</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
     </row>
@@ -1047,18 +1047,18 @@
         <v>25</v>
       </c>
       <c r="B29" s="4">
-        <v>100</v>
+        <v>340</v>
       </c>
       <c r="C29" s="4">
-        <f>10+(INT($A29/10))</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="D29" s="4">
-        <f>10+(INT($A29/10))</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="E29" s="4">
-        <f>10+(INT($A29/10))</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
     </row>
@@ -1067,18 +1067,18 @@
         <v>26</v>
       </c>
       <c r="B30" s="4">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="C30" s="4">
-        <f>10+(INT($A30/10))</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="D30" s="4">
-        <f>10+(INT($A30/10))</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="E30" s="4">
-        <f>10+(INT($A30/10))</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
     </row>
@@ -1087,18 +1087,18 @@
         <v>27</v>
       </c>
       <c r="B31" s="4">
-        <v>100</v>
+        <v>360</v>
       </c>
       <c r="C31" s="4">
-        <f>10+(INT($A31/10))</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="D31" s="4">
-        <f>10+(INT($A31/10))</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="E31" s="4">
-        <f>10+(INT($A31/10))</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
     </row>
@@ -1107,18 +1107,18 @@
         <v>28</v>
       </c>
       <c r="B32" s="4">
-        <v>100</v>
+        <v>370</v>
       </c>
       <c r="C32" s="4">
-        <f>10+(INT($A32/10))</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="D32" s="4">
-        <f>10+(INT($A32/10))</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="E32" s="4">
-        <f>10+(INT($A32/10))</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
     </row>
@@ -1127,18 +1127,18 @@
         <v>29</v>
       </c>
       <c r="B33" s="4">
-        <v>100</v>
+        <v>380</v>
       </c>
       <c r="C33" s="4">
-        <f>10+(INT($A33/10))</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="D33" s="4">
-        <f>10+(INT($A33/10))</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="E33" s="4">
-        <f>10+(INT($A33/10))</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
     </row>
@@ -1147,18 +1147,18 @@
         <v>30</v>
       </c>
       <c r="B34" s="4">
-        <v>100</v>
+        <v>390</v>
       </c>
       <c r="C34" s="4">
-        <f>10+(INT($A34/10))</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="D34" s="4">
-        <f>10+(INT($A34/10))</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="E34" s="4">
-        <f>10+(INT($A34/10))</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
     </row>
@@ -1167,18 +1167,18 @@
         <v>31</v>
       </c>
       <c r="B35" s="4">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="C35" s="4">
-        <f>10+(INT($A35/10))</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="D35" s="4">
-        <f>10+(INT($A35/10))</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="E35" s="4">
-        <f>10+(INT($A35/10))</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
     </row>
@@ -1187,18 +1187,18 @@
         <v>32</v>
       </c>
       <c r="B36" s="4">
-        <v>100</v>
+        <v>410</v>
       </c>
       <c r="C36" s="4">
-        <f>10+(INT($A36/10))</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="D36" s="4">
-        <f>10+(INT($A36/10))</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="E36" s="4">
-        <f>10+(INT($A36/10))</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
     </row>
@@ -1207,18 +1207,18 @@
         <v>33</v>
       </c>
       <c r="B37" s="4">
-        <v>100</v>
+        <v>420</v>
       </c>
       <c r="C37" s="4">
-        <f>10+(INT($A37/10))</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="D37" s="4">
-        <f>10+(INT($A37/10))</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="E37" s="4">
-        <f>10+(INT($A37/10))</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
     </row>
@@ -1227,18 +1227,18 @@
         <v>34</v>
       </c>
       <c r="B38" s="4">
-        <v>100</v>
+        <v>430</v>
       </c>
       <c r="C38" s="4">
-        <f>10+(INT($A38/10))</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="D38" s="4">
-        <f>10+(INT($A38/10))</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="E38" s="4">
-        <f>10+(INT($A38/10))</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
     </row>
@@ -1247,18 +1247,18 @@
         <v>35</v>
       </c>
       <c r="B39" s="4">
-        <v>100</v>
+        <v>440</v>
       </c>
       <c r="C39" s="4">
-        <f>10+(INT($A39/10))</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="D39" s="4">
-        <f>10+(INT($A39/10))</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="E39" s="4">
-        <f>10+(INT($A39/10))</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
     </row>
@@ -1267,18 +1267,18 @@
         <v>36</v>
       </c>
       <c r="B40" s="4">
-        <v>100</v>
+        <v>450</v>
       </c>
       <c r="C40" s="4">
-        <f>10+(INT($A40/10))</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="D40" s="4">
-        <f>10+(INT($A40/10))</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="E40" s="4">
-        <f>10+(INT($A40/10))</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
     </row>
@@ -1287,18 +1287,18 @@
         <v>37</v>
       </c>
       <c r="B41" s="4">
-        <v>100</v>
+        <v>460</v>
       </c>
       <c r="C41" s="4">
-        <f>10+(INT($A41/10))</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="D41" s="4">
-        <f>10+(INT($A41/10))</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="E41" s="4">
-        <f>10+(INT($A41/10))</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
     </row>
@@ -1307,18 +1307,18 @@
         <v>38</v>
       </c>
       <c r="B42" s="4">
-        <v>100</v>
+        <v>470</v>
       </c>
       <c r="C42" s="4">
-        <f>10+(INT($A42/10))</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="D42" s="4">
-        <f>10+(INT($A42/10))</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="E42" s="4">
-        <f>10+(INT($A42/10))</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
     </row>
@@ -1327,18 +1327,18 @@
         <v>39</v>
       </c>
       <c r="B43" s="4">
-        <v>100</v>
+        <v>480</v>
       </c>
       <c r="C43" s="4">
-        <f>10+(INT($A43/10))</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="D43" s="4">
-        <f>10+(INT($A43/10))</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="E43" s="4">
-        <f>10+(INT($A43/10))</f>
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
     </row>
@@ -1347,18 +1347,18 @@
         <v>40</v>
       </c>
       <c r="B44" s="4">
-        <v>100</v>
+        <v>490</v>
       </c>
       <c r="C44" s="4">
-        <f>10+(INT($A44/10))</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="D44" s="4">
-        <f>10+(INT($A44/10))</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
       <c r="E44" s="4">
-        <f>10+(INT($A44/10))</f>
+        <f t="shared" si="1"/>
         <v>14</v>
       </c>
     </row>
@@ -1367,18 +1367,18 @@
         <v>41</v>
       </c>
       <c r="B45" s="4">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="C45" s="4">
-        <f>10+(INT($A45/10))</f>
+        <f t="shared" ref="C45:E64" si="2">10+(INT($A45/10))</f>
         <v>14</v>
       </c>
       <c r="D45" s="4">
-        <f>10+(INT($A45/10))</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="E45" s="4">
-        <f>10+(INT($A45/10))</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
     </row>
@@ -1387,18 +1387,18 @@
         <v>42</v>
       </c>
       <c r="B46" s="4">
-        <v>100</v>
+        <v>510</v>
       </c>
       <c r="C46" s="4">
-        <f>10+(INT($A46/10))</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="D46" s="4">
-        <f>10+(INT($A46/10))</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="E46" s="4">
-        <f>10+(INT($A46/10))</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
     </row>
@@ -1407,18 +1407,18 @@
         <v>43</v>
       </c>
       <c r="B47" s="4">
-        <v>100</v>
+        <v>520</v>
       </c>
       <c r="C47" s="4">
-        <f>10+(INT($A47/10))</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="D47" s="4">
-        <f>10+(INT($A47/10))</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="E47" s="4">
-        <f>10+(INT($A47/10))</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
     </row>
@@ -1427,18 +1427,18 @@
         <v>44</v>
       </c>
       <c r="B48" s="4">
-        <v>100</v>
+        <v>530</v>
       </c>
       <c r="C48" s="4">
-        <f>10+(INT($A48/10))</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="D48" s="4">
-        <f>10+(INT($A48/10))</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="E48" s="4">
-        <f>10+(INT($A48/10))</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
     </row>
@@ -1447,18 +1447,18 @@
         <v>45</v>
       </c>
       <c r="B49" s="4">
-        <v>100</v>
+        <v>540</v>
       </c>
       <c r="C49" s="4">
-        <f>10+(INT($A49/10))</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="D49" s="4">
-        <f>10+(INT($A49/10))</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="E49" s="4">
-        <f>10+(INT($A49/10))</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
     </row>
@@ -1467,18 +1467,18 @@
         <v>46</v>
       </c>
       <c r="B50" s="4">
-        <v>100</v>
+        <v>550</v>
       </c>
       <c r="C50" s="4">
-        <f>10+(INT($A50/10))</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="D50" s="4">
-        <f>10+(INT($A50/10))</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="E50" s="4">
-        <f>10+(INT($A50/10))</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
     </row>
@@ -1487,18 +1487,18 @@
         <v>47</v>
       </c>
       <c r="B51" s="4">
-        <v>100</v>
+        <v>560</v>
       </c>
       <c r="C51" s="4">
-        <f>10+(INT($A51/10))</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="D51" s="4">
-        <f>10+(INT($A51/10))</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="E51" s="4">
-        <f>10+(INT($A51/10))</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
     </row>
@@ -1507,18 +1507,18 @@
         <v>48</v>
       </c>
       <c r="B52" s="4">
-        <v>100</v>
+        <v>570</v>
       </c>
       <c r="C52" s="4">
-        <f>10+(INT($A52/10))</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="D52" s="4">
-        <f>10+(INT($A52/10))</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="E52" s="4">
-        <f>10+(INT($A52/10))</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
     </row>
@@ -1527,18 +1527,18 @@
         <v>49</v>
       </c>
       <c r="B53" s="4">
-        <v>100</v>
+        <v>580</v>
       </c>
       <c r="C53" s="4">
-        <f>10+(INT($A53/10))</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="D53" s="4">
-        <f>10+(INT($A53/10))</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
       <c r="E53" s="4">
-        <f>10+(INT($A53/10))</f>
+        <f t="shared" si="2"/>
         <v>14</v>
       </c>
     </row>
@@ -1547,18 +1547,18 @@
         <v>50</v>
       </c>
       <c r="B54" s="4">
-        <v>100</v>
+        <v>590</v>
       </c>
       <c r="C54" s="4">
-        <f>10+(INT($A54/10))</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="D54" s="4">
-        <f>10+(INT($A54/10))</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="E54" s="4">
-        <f>10+(INT($A54/10))</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
     </row>
@@ -1567,18 +1567,18 @@
         <v>51</v>
       </c>
       <c r="B55" s="4">
-        <v>100</v>
+        <v>600</v>
       </c>
       <c r="C55" s="4">
-        <f>10+(INT($A55/10))</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="D55" s="4">
-        <f>10+(INT($A55/10))</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="E55" s="4">
-        <f>10+(INT($A55/10))</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
     </row>
@@ -1587,18 +1587,18 @@
         <v>52</v>
       </c>
       <c r="B56" s="4">
-        <v>100</v>
+        <v>610</v>
       </c>
       <c r="C56" s="4">
-        <f>10+(INT($A56/10))</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="D56" s="4">
-        <f>10+(INT($A56/10))</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="E56" s="4">
-        <f>10+(INT($A56/10))</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
     </row>
@@ -1607,18 +1607,18 @@
         <v>53</v>
       </c>
       <c r="B57" s="4">
-        <v>100</v>
+        <v>620</v>
       </c>
       <c r="C57" s="4">
-        <f>10+(INT($A57/10))</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="D57" s="4">
-        <f>10+(INT($A57/10))</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="E57" s="4">
-        <f>10+(INT($A57/10))</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
     </row>
@@ -1627,18 +1627,18 @@
         <v>54</v>
       </c>
       <c r="B58" s="4">
-        <v>100</v>
+        <v>630</v>
       </c>
       <c r="C58" s="4">
-        <f>10+(INT($A58/10))</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="D58" s="4">
-        <f>10+(INT($A58/10))</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="E58" s="4">
-        <f>10+(INT($A58/10))</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
     </row>
@@ -1647,18 +1647,18 @@
         <v>55</v>
       </c>
       <c r="B59" s="4">
-        <v>100</v>
+        <v>640</v>
       </c>
       <c r="C59" s="4">
-        <f>10+(INT($A59/10))</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="D59" s="4">
-        <f>10+(INT($A59/10))</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="E59" s="4">
-        <f>10+(INT($A59/10))</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
     </row>
@@ -1667,18 +1667,18 @@
         <v>56</v>
       </c>
       <c r="B60" s="4">
-        <v>100</v>
+        <v>650</v>
       </c>
       <c r="C60" s="4">
-        <f>10+(INT($A60/10))</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="D60" s="4">
-        <f>10+(INT($A60/10))</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="E60" s="4">
-        <f>10+(INT($A60/10))</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
     </row>
@@ -1687,18 +1687,18 @@
         <v>57</v>
       </c>
       <c r="B61" s="4">
-        <v>100</v>
+        <v>660</v>
       </c>
       <c r="C61" s="4">
-        <f>10+(INT($A61/10))</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="D61" s="4">
-        <f>10+(INT($A61/10))</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="E61" s="4">
-        <f>10+(INT($A61/10))</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
     </row>
@@ -1707,18 +1707,18 @@
         <v>58</v>
       </c>
       <c r="B62" s="4">
-        <v>100</v>
+        <v>670</v>
       </c>
       <c r="C62" s="4">
-        <f>10+(INT($A62/10))</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="D62" s="4">
-        <f>10+(INT($A62/10))</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="E62" s="4">
-        <f>10+(INT($A62/10))</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
     </row>
@@ -1727,18 +1727,18 @@
         <v>59</v>
       </c>
       <c r="B63" s="4">
-        <v>100</v>
+        <v>680</v>
       </c>
       <c r="C63" s="4">
-        <f>10+(INT($A63/10))</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="D63" s="4">
-        <f>10+(INT($A63/10))</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="E63" s="4">
-        <f>10+(INT($A63/10))</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
     </row>
@@ -1747,18 +1747,18 @@
         <v>60</v>
       </c>
       <c r="B64" s="4">
-        <v>100</v>
+        <v>690</v>
       </c>
       <c r="C64" s="4">
-        <f>10+(INT($A64/10))</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
       <c r="D64" s="4">
-        <f>10+(INT($A64/10))</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
       <c r="E64" s="4">
-        <f>10+(INT($A64/10))</f>
+        <f t="shared" si="2"/>
         <v>16</v>
       </c>
     </row>
@@ -1767,18 +1767,18 @@
         <v>61</v>
       </c>
       <c r="B65" s="4">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="C65" s="4">
-        <f>10+(INT($A65/10))</f>
+        <f t="shared" ref="C65:E84" si="3">10+(INT($A65/10))</f>
         <v>16</v>
       </c>
       <c r="D65" s="4">
-        <f>10+(INT($A65/10))</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="E65" s="4">
-        <f>10+(INT($A65/10))</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
     </row>
@@ -1787,18 +1787,18 @@
         <v>62</v>
       </c>
       <c r="B66" s="4">
-        <v>100</v>
+        <v>710</v>
       </c>
       <c r="C66" s="4">
-        <f>10+(INT($A66/10))</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="D66" s="4">
-        <f>10+(INT($A66/10))</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="E66" s="4">
-        <f>10+(INT($A66/10))</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
     </row>
@@ -1807,18 +1807,18 @@
         <v>63</v>
       </c>
       <c r="B67" s="4">
-        <v>100</v>
+        <v>720</v>
       </c>
       <c r="C67" s="4">
-        <f>10+(INT($A67/10))</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="D67" s="4">
-        <f>10+(INT($A67/10))</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="E67" s="4">
-        <f>10+(INT($A67/10))</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
     </row>
@@ -1827,18 +1827,18 @@
         <v>64</v>
       </c>
       <c r="B68" s="4">
-        <v>100</v>
+        <v>730</v>
       </c>
       <c r="C68" s="4">
-        <f>10+(INT($A68/10))</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="D68" s="4">
-        <f>10+(INT($A68/10))</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="E68" s="4">
-        <f>10+(INT($A68/10))</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
     </row>
@@ -1847,18 +1847,18 @@
         <v>65</v>
       </c>
       <c r="B69" s="4">
-        <v>100</v>
+        <v>740</v>
       </c>
       <c r="C69" s="4">
-        <f>10+(INT($A69/10))</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="D69" s="4">
-        <f>10+(INT($A69/10))</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="E69" s="4">
-        <f>10+(INT($A69/10))</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
     </row>
@@ -1867,18 +1867,18 @@
         <v>66</v>
       </c>
       <c r="B70" s="4">
-        <v>100</v>
+        <v>750</v>
       </c>
       <c r="C70" s="4">
-        <f>10+(INT($A70/10))</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="D70" s="4">
-        <f>10+(INT($A70/10))</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="E70" s="4">
-        <f>10+(INT($A70/10))</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
     </row>
@@ -1887,18 +1887,18 @@
         <v>67</v>
       </c>
       <c r="B71" s="4">
-        <v>100</v>
+        <v>760</v>
       </c>
       <c r="C71" s="4">
-        <f>10+(INT($A71/10))</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="D71" s="4">
-        <f>10+(INT($A71/10))</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="E71" s="4">
-        <f>10+(INT($A71/10))</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
     </row>
@@ -1907,18 +1907,18 @@
         <v>68</v>
       </c>
       <c r="B72" s="4">
-        <v>100</v>
+        <v>770</v>
       </c>
       <c r="C72" s="4">
-        <f>10+(INT($A72/10))</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="D72" s="4">
-        <f>10+(INT($A72/10))</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="E72" s="4">
-        <f>10+(INT($A72/10))</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
     </row>
@@ -1927,18 +1927,18 @@
         <v>69</v>
       </c>
       <c r="B73" s="4">
-        <v>100</v>
+        <v>780</v>
       </c>
       <c r="C73" s="4">
-        <f>10+(INT($A73/10))</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="D73" s="4">
-        <f>10+(INT($A73/10))</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
       <c r="E73" s="4">
-        <f>10+(INT($A73/10))</f>
+        <f t="shared" si="3"/>
         <v>16</v>
       </c>
     </row>
@@ -1947,18 +1947,18 @@
         <v>70</v>
       </c>
       <c r="B74" s="4">
-        <v>100</v>
+        <v>790</v>
       </c>
       <c r="C74" s="4">
-        <f>10+(INT($A74/10))</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="D74" s="4">
-        <f>10+(INT($A74/10))</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="E74" s="4">
-        <f>10+(INT($A74/10))</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
     </row>
@@ -1967,18 +1967,18 @@
         <v>71</v>
       </c>
       <c r="B75" s="4">
-        <v>100</v>
+        <v>800</v>
       </c>
       <c r="C75" s="4">
-        <f>10+(INT($A75/10))</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="D75" s="4">
-        <f>10+(INT($A75/10))</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="E75" s="4">
-        <f>10+(INT($A75/10))</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
     </row>
@@ -1987,18 +1987,18 @@
         <v>72</v>
       </c>
       <c r="B76" s="4">
-        <v>100</v>
+        <v>810</v>
       </c>
       <c r="C76" s="4">
-        <f>10+(INT($A76/10))</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="D76" s="4">
-        <f>10+(INT($A76/10))</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="E76" s="4">
-        <f>10+(INT($A76/10))</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
     </row>
@@ -2007,18 +2007,18 @@
         <v>73</v>
       </c>
       <c r="B77" s="4">
-        <v>100</v>
+        <v>820</v>
       </c>
       <c r="C77" s="4">
-        <f>10+(INT($A77/10))</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="D77" s="4">
-        <f>10+(INT($A77/10))</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="E77" s="4">
-        <f>10+(INT($A77/10))</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
     </row>
@@ -2027,18 +2027,18 @@
         <v>74</v>
       </c>
       <c r="B78" s="4">
-        <v>100</v>
+        <v>830</v>
       </c>
       <c r="C78" s="4">
-        <f>10+(INT($A78/10))</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="D78" s="4">
-        <f>10+(INT($A78/10))</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="E78" s="4">
-        <f>10+(INT($A78/10))</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
     </row>
@@ -2047,18 +2047,18 @@
         <v>75</v>
       </c>
       <c r="B79" s="4">
-        <v>100</v>
+        <v>840</v>
       </c>
       <c r="C79" s="4">
-        <f>10+(INT($A79/10))</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="D79" s="4">
-        <f>10+(INT($A79/10))</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="E79" s="4">
-        <f>10+(INT($A79/10))</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
     </row>
@@ -2067,18 +2067,18 @@
         <v>76</v>
       </c>
       <c r="B80" s="4">
-        <v>100</v>
+        <v>850</v>
       </c>
       <c r="C80" s="4">
-        <f>10+(INT($A80/10))</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="D80" s="4">
-        <f>10+(INT($A80/10))</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="E80" s="4">
-        <f>10+(INT($A80/10))</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
     </row>
@@ -2087,18 +2087,18 @@
         <v>77</v>
       </c>
       <c r="B81" s="4">
-        <v>100</v>
+        <v>860</v>
       </c>
       <c r="C81" s="4">
-        <f>10+(INT($A81/10))</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="D81" s="4">
-        <f>10+(INT($A81/10))</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="E81" s="4">
-        <f>10+(INT($A81/10))</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
     </row>
@@ -2107,18 +2107,18 @@
         <v>78</v>
       </c>
       <c r="B82" s="4">
-        <v>100</v>
+        <v>870</v>
       </c>
       <c r="C82" s="4">
-        <f>10+(INT($A82/10))</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="D82" s="4">
-        <f>10+(INT($A82/10))</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="E82" s="4">
-        <f>10+(INT($A82/10))</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
     </row>
@@ -2127,18 +2127,18 @@
         <v>79</v>
       </c>
       <c r="B83" s="4">
-        <v>100</v>
+        <v>880</v>
       </c>
       <c r="C83" s="4">
-        <f>10+(INT($A83/10))</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="D83" s="4">
-        <f>10+(INT($A83/10))</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
       <c r="E83" s="4">
-        <f>10+(INT($A83/10))</f>
+        <f t="shared" si="3"/>
         <v>17</v>
       </c>
     </row>
@@ -2147,18 +2147,18 @@
         <v>80</v>
       </c>
       <c r="B84" s="4">
-        <v>100</v>
+        <v>890</v>
       </c>
       <c r="C84" s="4">
-        <f>10+(INT($A84/10))</f>
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
       <c r="D84" s="4">
-        <f>10+(INT($A84/10))</f>
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
       <c r="E84" s="4">
-        <f>10+(INT($A84/10))</f>
+        <f t="shared" si="3"/>
         <v>18</v>
       </c>
     </row>
@@ -2167,18 +2167,18 @@
         <v>81</v>
       </c>
       <c r="B85" s="4">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="C85" s="4">
-        <f>10+(INT($A85/10))</f>
+        <f t="shared" ref="C85:E104" si="4">10+(INT($A85/10))</f>
         <v>18</v>
       </c>
       <c r="D85" s="4">
-        <f>10+(INT($A85/10))</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
       <c r="E85" s="4">
-        <f>10+(INT($A85/10))</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
     </row>
@@ -2187,18 +2187,18 @@
         <v>82</v>
       </c>
       <c r="B86" s="4">
-        <v>100</v>
+        <v>910</v>
       </c>
       <c r="C86" s="4">
-        <f>10+(INT($A86/10))</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
       <c r="D86" s="4">
-        <f>10+(INT($A86/10))</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
       <c r="E86" s="4">
-        <f>10+(INT($A86/10))</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
     </row>
@@ -2207,18 +2207,18 @@
         <v>83</v>
       </c>
       <c r="B87" s="4">
-        <v>100</v>
+        <v>920</v>
       </c>
       <c r="C87" s="4">
-        <f>10+(INT($A87/10))</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
       <c r="D87" s="4">
-        <f>10+(INT($A87/10))</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
       <c r="E87" s="4">
-        <f>10+(INT($A87/10))</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
     </row>
@@ -2227,18 +2227,18 @@
         <v>84</v>
       </c>
       <c r="B88" s="4">
-        <v>100</v>
+        <v>930</v>
       </c>
       <c r="C88" s="4">
-        <f>10+(INT($A88/10))</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
       <c r="D88" s="4">
-        <f>10+(INT($A88/10))</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
       <c r="E88" s="4">
-        <f>10+(INT($A88/10))</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
     </row>
@@ -2247,18 +2247,18 @@
         <v>85</v>
       </c>
       <c r="B89" s="4">
-        <v>100</v>
+        <v>940</v>
       </c>
       <c r="C89" s="4">
-        <f>10+(INT($A89/10))</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
       <c r="D89" s="4">
-        <f>10+(INT($A89/10))</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
       <c r="E89" s="4">
-        <f>10+(INT($A89/10))</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
     </row>
@@ -2267,18 +2267,18 @@
         <v>86</v>
       </c>
       <c r="B90" s="4">
-        <v>100</v>
+        <v>950</v>
       </c>
       <c r="C90" s="4">
-        <f>10+(INT($A90/10))</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
       <c r="D90" s="4">
-        <f>10+(INT($A90/10))</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
       <c r="E90" s="4">
-        <f>10+(INT($A90/10))</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
     </row>
@@ -2287,18 +2287,18 @@
         <v>87</v>
       </c>
       <c r="B91" s="4">
-        <v>100</v>
+        <v>960</v>
       </c>
       <c r="C91" s="4">
-        <f>10+(INT($A91/10))</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
       <c r="D91" s="4">
-        <f>10+(INT($A91/10))</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
       <c r="E91" s="4">
-        <f>10+(INT($A91/10))</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
     </row>
@@ -2307,18 +2307,18 @@
         <v>88</v>
       </c>
       <c r="B92" s="4">
-        <v>100</v>
+        <v>970</v>
       </c>
       <c r="C92" s="4">
-        <f>10+(INT($A92/10))</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
       <c r="D92" s="4">
-        <f>10+(INT($A92/10))</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
       <c r="E92" s="4">
-        <f>10+(INT($A92/10))</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
     </row>
@@ -2327,18 +2327,18 @@
         <v>89</v>
       </c>
       <c r="B93" s="4">
-        <v>100</v>
+        <v>980</v>
       </c>
       <c r="C93" s="4">
-        <f>10+(INT($A93/10))</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
       <c r="D93" s="4">
-        <f>10+(INT($A93/10))</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
       <c r="E93" s="4">
-        <f>10+(INT($A93/10))</f>
+        <f t="shared" si="4"/>
         <v>18</v>
       </c>
     </row>
@@ -2347,18 +2347,18 @@
         <v>90</v>
       </c>
       <c r="B94" s="4">
-        <v>100</v>
+        <v>990</v>
       </c>
       <c r="C94" s="4">
-        <f>10+(INT($A94/10))</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="D94" s="4">
-        <f>10+(INT($A94/10))</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="E94" s="4">
-        <f>10+(INT($A94/10))</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
     </row>
@@ -2367,18 +2367,18 @@
         <v>91</v>
       </c>
       <c r="B95" s="4">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="C95" s="4">
-        <f>10+(INT($A95/10))</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="D95" s="4">
-        <f>10+(INT($A95/10))</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="E95" s="4">
-        <f>10+(INT($A95/10))</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
     </row>
@@ -2387,18 +2387,18 @@
         <v>92</v>
       </c>
       <c r="B96" s="4">
-        <v>100</v>
+        <v>1010</v>
       </c>
       <c r="C96" s="4">
-        <f>10+(INT($A96/10))</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="D96" s="4">
-        <f>10+(INT($A96/10))</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="E96" s="4">
-        <f>10+(INT($A96/10))</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
     </row>
@@ -2407,18 +2407,18 @@
         <v>93</v>
       </c>
       <c r="B97" s="4">
-        <v>100</v>
+        <v>1020</v>
       </c>
       <c r="C97" s="4">
-        <f>10+(INT($A97/10))</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="D97" s="4">
-        <f>10+(INT($A97/10))</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="E97" s="4">
-        <f>10+(INT($A97/10))</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
     </row>
@@ -2427,18 +2427,18 @@
         <v>94</v>
       </c>
       <c r="B98" s="4">
-        <v>100</v>
+        <v>1030</v>
       </c>
       <c r="C98" s="4">
-        <f>10+(INT($A98/10))</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="D98" s="4">
-        <f>10+(INT($A98/10))</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="E98" s="4">
-        <f>10+(INT($A98/10))</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
     </row>
@@ -2447,18 +2447,18 @@
         <v>95</v>
       </c>
       <c r="B99" s="4">
-        <v>100</v>
+        <v>1040</v>
       </c>
       <c r="C99" s="4">
-        <f>10+(INT($A99/10))</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="D99" s="4">
-        <f>10+(INT($A99/10))</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="E99" s="4">
-        <f>10+(INT($A99/10))</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
     </row>
@@ -2467,18 +2467,18 @@
         <v>96</v>
       </c>
       <c r="B100" s="4">
-        <v>100</v>
+        <v>1050</v>
       </c>
       <c r="C100" s="4">
-        <f>10+(INT($A100/10))</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="D100" s="4">
-        <f>10+(INT($A100/10))</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="E100" s="4">
-        <f>10+(INT($A100/10))</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
     </row>
@@ -2487,18 +2487,18 @@
         <v>97</v>
       </c>
       <c r="B101" s="4">
-        <v>100</v>
+        <v>1060</v>
       </c>
       <c r="C101" s="4">
-        <f>10+(INT($A101/10))</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="D101" s="4">
-        <f>10+(INT($A101/10))</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="E101" s="4">
-        <f>10+(INT($A101/10))</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
     </row>
@@ -2507,18 +2507,18 @@
         <v>98</v>
       </c>
       <c r="B102" s="4">
-        <v>100</v>
+        <v>1070</v>
       </c>
       <c r="C102" s="4">
-        <f>10+(INT($A102/10))</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="D102" s="4">
-        <f>10+(INT($A102/10))</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="E102" s="4">
-        <f>10+(INT($A102/10))</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
     </row>
@@ -2527,18 +2527,18 @@
         <v>99</v>
       </c>
       <c r="B103" s="4">
-        <v>100</v>
+        <v>1080</v>
       </c>
       <c r="C103" s="4">
-        <f>10+(INT($A103/10))</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="D103" s="4">
-        <f>10+(INT($A103/10))</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
       <c r="E103" s="4">
-        <f>10+(INT($A103/10))</f>
+        <f t="shared" si="4"/>
         <v>19</v>
       </c>
     </row>
@@ -2547,18 +2547,18 @@
         <v>100</v>
       </c>
       <c r="B104" s="4">
-        <v>100</v>
+        <v>1090</v>
       </c>
       <c r="C104" s="4">
-        <f>10+(INT($A104/10))</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="D104" s="4">
-        <f>10+(INT($A104/10))</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
       <c r="E104" s="4">
-        <f>10+(INT($A104/10))</f>
+        <f t="shared" si="4"/>
         <v>20</v>
       </c>
     </row>

--- a/Design/config/CityLevelConfig.xlsx
+++ b/Design/config/CityLevelConfig.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
   <si>
     <t>序列</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -87,6 +87,14 @@
   </si>
   <si>
     <t>SoldierAdd</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>工位数</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>JobCount</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -508,6 +516,9 @@
       <c r="E1" s="3" t="s">
         <v>15</v>
       </c>
+      <c r="F1" s="3" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
@@ -525,6 +536,9 @@
       <c r="E2" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="F2" s="2" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
@@ -542,6 +556,9 @@
       <c r="E3" s="2" t="s">
         <v>14</v>
       </c>
+      <c r="F3" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
@@ -559,6 +576,9 @@
       <c r="E4" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="F4" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
@@ -568,7 +588,7 @@
         <v>100</v>
       </c>
       <c r="C5" s="4">
-        <f t="shared" ref="C5:E24" si="0">10+(INT($A5/10))</f>
+        <f t="shared" ref="C5:F24" si="0">10+(INT($A5/10))</f>
         <v>10</v>
       </c>
       <c r="D5" s="4">
@@ -578,6 +598,9 @@
       <c r="E5" s="4">
         <f t="shared" si="0"/>
         <v>10</v>
+      </c>
+      <c r="F5" s="4">
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.2">
@@ -599,6 +622,9 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
+      <c r="F6" s="4">
+        <v>4</v>
+      </c>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
@@ -619,6 +645,9 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
+      <c r="F7" s="4">
+        <v>4</v>
+      </c>
       <c r="V7" s="5"/>
       <c r="W7" s="5"/>
     </row>
@@ -641,6 +670,9 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
+      <c r="F8" s="4">
+        <v>4</v>
+      </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
@@ -661,6 +693,9 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
+      <c r="F9" s="4">
+        <v>4</v>
+      </c>
     </row>
     <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
@@ -681,6 +716,9 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
+      <c r="F10" s="4">
+        <v>4</v>
+      </c>
     </row>
     <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
@@ -701,6 +739,9 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
+      <c r="F11" s="4">
+        <v>4</v>
+      </c>
     </row>
     <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
@@ -720,6 +761,9 @@
       <c r="E12" s="4">
         <f t="shared" si="0"/>
         <v>10</v>
+      </c>
+      <c r="F12" s="4">
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:23" x14ac:dyDescent="0.2">
@@ -741,6 +785,9 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
+      <c r="F13" s="4">
+        <v>4</v>
+      </c>
     </row>
     <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A14" s="4">
@@ -761,6 +808,9 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
+      <c r="F14" s="4">
+        <v>5</v>
+      </c>
     </row>
     <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A15" s="4">
@@ -781,6 +831,9 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
+      <c r="F15" s="4">
+        <v>5</v>
+      </c>
     </row>
     <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A16" s="4">
@@ -801,8 +854,11 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F16" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" s="4">
         <v>13</v>
       </c>
@@ -821,8 +877,11 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F17" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" s="4">
         <v>14</v>
       </c>
@@ -841,8 +900,11 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F18" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" s="4">
         <v>15</v>
       </c>
@@ -861,8 +923,11 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F19" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" s="4">
         <v>16</v>
       </c>
@@ -881,8 +946,11 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F20" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" s="4">
         <v>17</v>
       </c>
@@ -901,8 +969,11 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F21" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" s="4">
         <v>18</v>
       </c>
@@ -921,8 +992,11 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F22" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" s="4">
         <v>19</v>
       </c>
@@ -941,8 +1015,11 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F23" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A24" s="4">
         <v>20</v>
       </c>
@@ -961,8 +1038,11 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F24" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A25" s="4">
         <v>21</v>
       </c>
@@ -970,7 +1050,7 @@
         <v>300</v>
       </c>
       <c r="C25" s="4">
-        <f t="shared" ref="C25:E44" si="1">10+(INT($A25/10))</f>
+        <f t="shared" ref="C25:F44" si="1">10+(INT($A25/10))</f>
         <v>12</v>
       </c>
       <c r="D25" s="4">
@@ -981,8 +1061,11 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F25" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A26" s="4">
         <v>22</v>
       </c>
@@ -1001,8 +1084,11 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F26" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A27" s="4">
         <v>23</v>
       </c>
@@ -1021,8 +1107,11 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F27" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A28" s="4">
         <v>24</v>
       </c>
@@ -1041,8 +1130,11 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F28" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A29" s="4">
         <v>25</v>
       </c>
@@ -1061,8 +1153,11 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F29" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A30" s="4">
         <v>26</v>
       </c>
@@ -1081,8 +1176,11 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F30" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" s="4">
         <v>27</v>
       </c>
@@ -1101,8 +1199,11 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F31" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" s="4">
         <v>28</v>
       </c>
@@ -1121,8 +1222,11 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F32" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="4">
         <v>29</v>
       </c>
@@ -1141,8 +1245,11 @@
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F33" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="4">
         <v>30</v>
       </c>
@@ -1161,8 +1268,11 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F34" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="4">
         <v>31</v>
       </c>
@@ -1181,8 +1291,11 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F35" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="4">
         <v>32</v>
       </c>
@@ -1201,8 +1314,11 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F36" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
         <v>33</v>
       </c>
@@ -1221,8 +1337,11 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F37" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
         <v>34</v>
       </c>
@@ -1241,8 +1360,11 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F38" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A39" s="4">
         <v>35</v>
       </c>
@@ -1261,8 +1383,11 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F39" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
         <v>36</v>
       </c>
@@ -1281,8 +1406,11 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F40" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
         <v>37</v>
       </c>
@@ -1301,8 +1429,11 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F41" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="4">
         <v>38</v>
       </c>
@@ -1321,8 +1452,11 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F42" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="4">
         <v>39</v>
       </c>
@@ -1341,8 +1475,11 @@
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F43" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="4">
         <v>40</v>
       </c>
@@ -1361,8 +1498,11 @@
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F44" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A45" s="4">
         <v>41</v>
       </c>
@@ -1370,7 +1510,7 @@
         <v>500</v>
       </c>
       <c r="C45" s="4">
-        <f t="shared" ref="C45:E64" si="2">10+(INT($A45/10))</f>
+        <f t="shared" ref="C45:F64" si="2">10+(INT($A45/10))</f>
         <v>14</v>
       </c>
       <c r="D45" s="4">
@@ -1381,8 +1521,11 @@
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F45" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A46" s="4">
         <v>42</v>
       </c>
@@ -1401,8 +1544,11 @@
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F46" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A47" s="4">
         <v>43</v>
       </c>
@@ -1421,8 +1567,11 @@
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F47" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A48" s="4">
         <v>44</v>
       </c>
@@ -1441,8 +1590,11 @@
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F48" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" s="4">
         <v>45</v>
       </c>
@@ -1461,8 +1613,11 @@
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F49" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="4">
         <v>46</v>
       </c>
@@ -1481,8 +1636,11 @@
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F50" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" s="4">
         <v>47</v>
       </c>
@@ -1501,8 +1659,11 @@
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F51" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" s="4">
         <v>48</v>
       </c>
@@ -1521,8 +1682,11 @@
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F52" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" s="4">
         <v>49</v>
       </c>
@@ -1541,8 +1705,11 @@
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F53" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" s="4">
         <v>50</v>
       </c>
@@ -1561,8 +1728,11 @@
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F54" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A55" s="4">
         <v>51</v>
       </c>
@@ -1581,8 +1751,11 @@
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F55" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" s="4">
         <v>52</v>
       </c>
@@ -1601,8 +1774,11 @@
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F56" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" s="4">
         <v>53</v>
       </c>
@@ -1621,8 +1797,11 @@
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F57" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" s="4">
         <v>54</v>
       </c>
@@ -1641,8 +1820,11 @@
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F58" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A59" s="4">
         <v>55</v>
       </c>
@@ -1661,8 +1843,11 @@
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F59" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A60" s="4">
         <v>56</v>
       </c>
@@ -1681,8 +1866,11 @@
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F60" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" s="4">
         <v>57</v>
       </c>
@@ -1701,8 +1889,11 @@
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F61" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" s="4">
         <v>58</v>
       </c>
@@ -1721,8 +1912,11 @@
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F62" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" s="4">
         <v>59</v>
       </c>
@@ -1741,8 +1935,11 @@
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F63" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" s="4">
         <v>60</v>
       </c>
@@ -1761,8 +1958,11 @@
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F64" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A65" s="4">
         <v>61</v>
       </c>
@@ -1770,7 +1970,7 @@
         <v>700</v>
       </c>
       <c r="C65" s="4">
-        <f t="shared" ref="C65:E84" si="3">10+(INT($A65/10))</f>
+        <f t="shared" ref="C65:F84" si="3">10+(INT($A65/10))</f>
         <v>16</v>
       </c>
       <c r="D65" s="4">
@@ -1781,8 +1981,11 @@
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F65" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" s="4">
         <v>62</v>
       </c>
@@ -1801,8 +2004,11 @@
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F66" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" s="4">
         <v>63</v>
       </c>
@@ -1821,8 +2027,11 @@
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F67" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" s="4">
         <v>64</v>
       </c>
@@ -1841,8 +2050,11 @@
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F68" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" s="4">
         <v>65</v>
       </c>
@@ -1861,8 +2073,11 @@
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F69" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" s="4">
         <v>66</v>
       </c>
@@ -1881,8 +2096,11 @@
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F70" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" s="4">
         <v>67</v>
       </c>
@@ -1901,8 +2119,11 @@
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F71" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" s="4">
         <v>68</v>
       </c>
@@ -1921,8 +2142,11 @@
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F72" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A73" s="4">
         <v>69</v>
       </c>
@@ -1941,8 +2165,11 @@
         <f t="shared" si="3"/>
         <v>16</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F73" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" s="4">
         <v>70</v>
       </c>
@@ -1961,8 +2188,11 @@
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F74" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" s="4">
         <v>71</v>
       </c>
@@ -1981,8 +2211,11 @@
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F75" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" s="4">
         <v>72</v>
       </c>
@@ -2001,8 +2234,11 @@
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F76" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" s="4">
         <v>73</v>
       </c>
@@ -2021,8 +2257,11 @@
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F77" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" s="4">
         <v>74</v>
       </c>
@@ -2041,8 +2280,11 @@
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F78" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" s="4">
         <v>75</v>
       </c>
@@ -2061,8 +2303,11 @@
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F79" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" s="4">
         <v>76</v>
       </c>
@@ -2081,8 +2326,11 @@
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F80" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" s="4">
         <v>77</v>
       </c>
@@ -2101,8 +2349,11 @@
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F81" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" s="4">
         <v>78</v>
       </c>
@@ -2121,8 +2372,11 @@
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F82" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" s="4">
         <v>79</v>
       </c>
@@ -2141,8 +2395,11 @@
         <f t="shared" si="3"/>
         <v>17</v>
       </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F83" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" s="4">
         <v>80</v>
       </c>
@@ -2161,8 +2418,11 @@
         <f t="shared" si="3"/>
         <v>18</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F84" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" s="4">
         <v>81</v>
       </c>
@@ -2170,7 +2430,7 @@
         <v>900</v>
       </c>
       <c r="C85" s="4">
-        <f t="shared" ref="C85:E104" si="4">10+(INT($A85/10))</f>
+        <f t="shared" ref="C85:F104" si="4">10+(INT($A85/10))</f>
         <v>18</v>
       </c>
       <c r="D85" s="4">
@@ -2181,8 +2441,11 @@
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F85" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" s="4">
         <v>82</v>
       </c>
@@ -2201,8 +2464,11 @@
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F86" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" s="4">
         <v>83</v>
       </c>
@@ -2221,8 +2487,11 @@
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F87" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" s="4">
         <v>84</v>
       </c>
@@ -2241,8 +2510,11 @@
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F88" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" s="4">
         <v>85</v>
       </c>
@@ -2261,8 +2533,11 @@
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F89" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" s="4">
         <v>86</v>
       </c>
@@ -2281,8 +2556,11 @@
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F90" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" s="4">
         <v>87</v>
       </c>
@@ -2301,8 +2579,11 @@
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F91" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" s="4">
         <v>88</v>
       </c>
@@ -2321,8 +2602,11 @@
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F92" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" s="4">
         <v>89</v>
       </c>
@@ -2341,8 +2625,11 @@
         <f t="shared" si="4"/>
         <v>18</v>
       </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F93" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" s="4">
         <v>90</v>
       </c>
@@ -2361,8 +2648,11 @@
         <f t="shared" si="4"/>
         <v>19</v>
       </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F94" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" s="4">
         <v>91</v>
       </c>
@@ -2381,8 +2671,11 @@
         <f t="shared" si="4"/>
         <v>19</v>
       </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F95" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" s="4">
         <v>92</v>
       </c>
@@ -2401,8 +2694,11 @@
         <f t="shared" si="4"/>
         <v>19</v>
       </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F96" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A97" s="4">
         <v>93</v>
       </c>
@@ -2421,8 +2717,11 @@
         <f t="shared" si="4"/>
         <v>19</v>
       </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F97" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A98" s="4">
         <v>94</v>
       </c>
@@ -2441,8 +2740,11 @@
         <f t="shared" si="4"/>
         <v>19</v>
       </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F98" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A99" s="4">
         <v>95</v>
       </c>
@@ -2461,8 +2763,11 @@
         <f t="shared" si="4"/>
         <v>19</v>
       </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F99" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A100" s="4">
         <v>96</v>
       </c>
@@ -2481,8 +2786,11 @@
         <f t="shared" si="4"/>
         <v>19</v>
       </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F100" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A101" s="4">
         <v>97</v>
       </c>
@@ -2501,8 +2809,11 @@
         <f t="shared" si="4"/>
         <v>19</v>
       </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F101" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A102" s="4">
         <v>98</v>
       </c>
@@ -2521,8 +2832,11 @@
         <f t="shared" si="4"/>
         <v>19</v>
       </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F102" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A103" s="4">
         <v>99</v>
       </c>
@@ -2541,8 +2855,11 @@
         <f t="shared" si="4"/>
         <v>19</v>
       </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F103" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A104" s="4">
         <v>100</v>
       </c>
@@ -2560,6 +2877,9 @@
       <c r="E104" s="4">
         <f t="shared" si="4"/>
         <v>20</v>
+      </c>
+      <c r="F104" s="4">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
